--- a/public/Examination/考核应用报表导出模板_202604091814.xlsx
+++ b/public/Examination/考核应用报表导出模板_202604091814.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43EE465-31E3-468B-8A8C-F10659843BD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3991E240-6463-4331-978F-C20FD5FC61CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,15 +11,15 @@
     <sheet name="评估组1-定量指标" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'评估组1-定量指标'!$A$2:$R$79</definedName>
-    <definedName name="_xlnm._FilterDatabase">'评估组1-定量指标'!$A$2:$R$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'评估组1-定量指标'!$A$2:$R$85</definedName>
+    <definedName name="_xlnm._FilterDatabase">'评估组1-定量指标'!$A$2:$R$73</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="287">
   <si>
     <t>HR备注：</t>
   </si>
@@ -549,9 +549,6 @@
   </si>
   <si>
     <t>OBM000110</t>
-  </si>
-  <si>
-    <t>金扬森</t>
   </si>
   <si>
     <t>销售收入达成率（抖音）</t>
@@ -956,6 +953,16 @@
   <si>
     <t>短视频商品点击达成率</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>周智超</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新开达人数</t>
+  </si>
+  <si>
+    <t>达人活跃数</t>
   </si>
 </sst>
 </file>
@@ -1365,7 +1372,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R83"/>
+  <dimension ref="A1:R85"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="51.625" customWidth="1"/>
@@ -1612,13 +1619,13 @@
         <v>26</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -1662,13 +1669,13 @@
         <v>26</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>44</v>
@@ -1762,7 +1769,7 @@
         <v>26</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>50</v>
@@ -1906,7 +1913,7 @@
         <v>58</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -1915,7 +1922,7 @@
         <v>60</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F12" s="12" t="s">
         <v>61</v>
@@ -3081,7 +3088,7 @@
         <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E38" t="s">
         <v>138</v>
@@ -3309,13 +3316,13 @@
         <v>26</v>
       </c>
       <c r="D44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E44" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G44" t="s">
         <v>163</v>
@@ -3341,25 +3348,25 @@
         <v>164</v>
       </c>
       <c r="B45" t="s">
-        <v>165</v>
+        <v>284</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>166</v>
+        <v>285</v>
       </c>
       <c r="E45" t="s">
+        <v>285</v>
+      </c>
+      <c r="F45" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="G45" t="s">
         <v>168</v>
       </c>
-      <c r="G45" t="s">
+      <c r="H45" t="s">
         <v>169</v>
-      </c>
-      <c r="H45" t="s">
-        <v>170</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3376,28 +3383,28 @@
     </row>
     <row r="46" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
-        <v>172</v>
+        <v>284</v>
       </c>
       <c r="C46" t="s">
         <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="E46" t="s">
+        <v>286</v>
+      </c>
+      <c r="F46" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="F46" s="12" t="s">
-        <v>173</v>
-      </c>
       <c r="G46" t="s">
+        <v>168</v>
+      </c>
+      <c r="H46" t="s">
         <v>169</v>
-      </c>
-      <c r="H46" t="s">
-        <v>170</v>
       </c>
       <c r="I46">
         <v>0</v>
@@ -3414,28 +3421,28 @@
     </row>
     <row r="47" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
-        <v>256</v>
+        <v>284</v>
       </c>
       <c r="C47" t="s">
         <v>26</v>
       </c>
       <c r="D47" t="s">
+        <v>165</v>
+      </c>
+      <c r="E47" t="s">
         <v>166</v>
       </c>
-      <c r="E47" t="s">
-        <v>257</v>
-      </c>
       <c r="F47" s="12" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="G47" t="s">
+        <v>168</v>
+      </c>
+      <c r="H47" t="s">
         <v>169</v>
-      </c>
-      <c r="H47" t="s">
-        <v>170</v>
       </c>
       <c r="I47">
         <v>0</v>
@@ -3452,28 +3459,28 @@
     </row>
     <row r="48" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>170</v>
       </c>
       <c r="B48" t="s">
-        <v>65</v>
+        <v>171</v>
       </c>
       <c r="C48" t="s">
         <v>26</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="E48" t="s">
-        <v>141</v>
+        <v>166</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="G48" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I48">
         <v>0</v>
@@ -3490,28 +3497,28 @@
     </row>
     <row r="49" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="B49" t="s">
-        <v>65</v>
+        <v>255</v>
       </c>
       <c r="C49" t="s">
         <v>26</v>
       </c>
       <c r="D49" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E49" t="s">
-        <v>147</v>
+        <v>256</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="G49" t="s">
-        <v>125</v>
+        <v>168</v>
       </c>
       <c r="H49" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="I49">
         <v>0</v>
@@ -3528,28 +3535,28 @@
     </row>
     <row r="50" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="B50" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="E50" t="s">
-        <v>181</v>
+        <v>141</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="G50" t="s">
-        <v>183</v>
+        <v>121</v>
       </c>
       <c r="H50" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3566,28 +3573,28 @@
     </row>
     <row r="51" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
-        <v>179</v>
+        <v>64</v>
       </c>
       <c r="B51" t="s">
-        <v>180</v>
+        <v>65</v>
       </c>
       <c r="C51" t="s">
         <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="E51" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G51" t="s">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="H51" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3604,28 +3611,28 @@
     </row>
     <row r="52" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
+        <v>178</v>
+      </c>
+      <c r="B52" t="s">
         <v>179</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
+        <v>26</v>
+      </c>
+      <c r="D52" t="s">
         <v>180</v>
       </c>
-      <c r="C52" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" t="s">
-        <v>187</v>
-      </c>
       <c r="E52" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="G52" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="H52" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3642,28 +3649,28 @@
     </row>
     <row r="53" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
+        <v>178</v>
+      </c>
+      <c r="B53" t="s">
         <v>179</v>
       </c>
-      <c r="B53" t="s">
-        <v>180</v>
-      </c>
       <c r="C53" t="s">
         <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>268</v>
+        <v>184</v>
       </c>
       <c r="E53" t="s">
-        <v>268</v>
+        <v>184</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>276</v>
+        <v>185</v>
       </c>
       <c r="G53" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="H53" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -3680,28 +3687,28 @@
     </row>
     <row r="54" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="C54" t="s">
         <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>86</v>
+        <v>186</v>
       </c>
       <c r="E54" t="s">
-        <v>262</v>
+        <v>186</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G54" t="s">
-        <v>142</v>
+        <v>188</v>
       </c>
       <c r="H54" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="I54">
         <v>0</v>
@@ -3718,28 +3725,28 @@
     </row>
     <row r="55" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="C55" t="s">
         <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>119</v>
+        <v>267</v>
       </c>
       <c r="E55" t="s">
-        <v>144</v>
+        <v>267</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>194</v>
+        <v>275</v>
       </c>
       <c r="G55" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="H55" t="s">
-        <v>143</v>
+        <v>190</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3765,19 +3772,19 @@
         <v>26</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="E56" t="s">
-        <v>147</v>
+        <v>261</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="G56" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H56" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3794,28 +3801,28 @@
     </row>
     <row r="57" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
-        <v>196</v>
+        <v>91</v>
       </c>
       <c r="B57" t="s">
-        <v>258</v>
+        <v>92</v>
       </c>
       <c r="C57" t="s">
         <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="E57" t="s">
-        <v>257</v>
+        <v>144</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G57" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="H57" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3832,28 +3839,28 @@
     </row>
     <row r="58" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
-        <v>198</v>
+        <v>91</v>
       </c>
       <c r="B58" t="s">
-        <v>199</v>
+        <v>92</v>
       </c>
       <c r="C58" t="s">
         <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>200</v>
+        <v>146</v>
       </c>
       <c r="E58" t="s">
-        <v>200</v>
+        <v>147</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="G58" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="H58" t="s">
-        <v>63</v>
+        <v>149</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3870,28 +3877,28 @@
     </row>
     <row r="59" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B59" t="s">
-        <v>203</v>
+        <v>257</v>
       </c>
       <c r="C59" t="s">
         <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E59" t="s">
-        <v>167</v>
+        <v>256</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="G59" t="s">
+        <v>168</v>
+      </c>
+      <c r="H59" t="s">
         <v>169</v>
-      </c>
-      <c r="H59" t="s">
-        <v>170</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3908,28 +3915,28 @@
     </row>
     <row r="60" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="B60" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="C60" t="s">
         <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="E60" t="s">
-        <v>257</v>
+        <v>199</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="G60" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="H60" t="s">
-        <v>170</v>
+        <v>63</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3946,28 +3953,28 @@
     </row>
     <row r="61" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>201</v>
       </c>
       <c r="B61" t="s">
-        <v>259</v>
+        <v>202</v>
       </c>
       <c r="C61" t="s">
         <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="E61" t="s">
-        <v>260</v>
+        <v>166</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="G61" t="s">
-        <v>210</v>
+        <v>168</v>
       </c>
       <c r="H61" t="s">
-        <v>211</v>
+        <v>169</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3984,28 +3991,28 @@
     </row>
     <row r="62" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="B62" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="C62" t="s">
         <v>26</v>
       </c>
       <c r="D62" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="E62" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="G62" t="s">
-        <v>214</v>
+        <v>168</v>
       </c>
       <c r="H62" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -4022,28 +4029,28 @@
     </row>
     <row r="63" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B63" t="s">
-        <v>72</v>
+        <v>258</v>
       </c>
       <c r="C63" t="s">
         <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>119</v>
+        <v>207</v>
       </c>
       <c r="E63" t="s">
-        <v>141</v>
+        <v>259</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="G63" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="H63" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4060,25 +4067,25 @@
     </row>
     <row r="64" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>258</v>
       </c>
       <c r="C64" t="s">
         <v>26</v>
       </c>
       <c r="D64" t="s">
-        <v>147</v>
+        <v>211</v>
       </c>
       <c r="E64" t="s">
-        <v>147</v>
+        <v>260</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="G64" t="s">
-        <v>125</v>
+        <v>213</v>
       </c>
       <c r="H64" t="s">
         <v>137</v>
@@ -4098,28 +4105,28 @@
     </row>
     <row r="65" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C65" t="s">
         <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="E65" t="s">
         <v>141</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G65" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H65" t="s">
-        <v>177</v>
+        <v>143</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4136,10 +4143,10 @@
     </row>
     <row r="66" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B66" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C66" t="s">
         <v>26</v>
@@ -4151,7 +4158,7 @@
         <v>147</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="G66" t="s">
         <v>125</v>
@@ -4174,28 +4181,28 @@
     </row>
     <row r="67" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
         <v>26</v>
       </c>
       <c r="D67" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="E67" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="G67" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="H67" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4212,28 +4219,28 @@
     </row>
     <row r="68" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C68" t="s">
         <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>119</v>
+        <v>147</v>
       </c>
       <c r="E68" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G68" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="H68" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4259,19 +4266,19 @@
         <v>26</v>
       </c>
       <c r="D69" t="s">
-        <v>146</v>
+        <v>86</v>
       </c>
       <c r="E69" t="s">
-        <v>147</v>
+        <v>86</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G69" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H69" t="s">
-        <v>149</v>
+        <v>192</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4288,28 +4295,28 @@
     </row>
     <row r="70" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B70" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C70" t="s">
         <v>26</v>
       </c>
       <c r="D70" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="E70" t="s">
-        <v>222</v>
+        <v>144</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="G70" t="s">
-        <v>169</v>
+        <v>142</v>
       </c>
       <c r="H70" t="s">
-        <v>170</v>
+        <v>143</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4326,190 +4333,154 @@
     </row>
     <row r="71" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
+        <v>94</v>
+      </c>
+      <c r="B71" t="s">
+        <v>95</v>
+      </c>
+      <c r="C71" t="s">
+        <v>26</v>
+      </c>
+      <c r="D71" t="s">
+        <v>146</v>
+      </c>
+      <c r="E71" t="s">
+        <v>147</v>
+      </c>
+      <c r="F71" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="G71" t="s">
+        <v>121</v>
+      </c>
+      <c r="H71" t="s">
+        <v>149</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A72" t="s">
         <v>79</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>80</v>
       </c>
-      <c r="C71" t="s">
-        <v>26</v>
-      </c>
-      <c r="D71" t="s">
-        <v>224</v>
-      </c>
-      <c r="E71" t="s">
-        <v>225</v>
-      </c>
-      <c r="F71" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="G71" t="s">
-        <v>227</v>
-      </c>
-      <c r="H71" t="s">
-        <v>228</v>
-      </c>
-      <c r="I71">
-        <v>0</v>
-      </c>
-      <c r="K71">
-        <v>0</v>
-      </c>
-      <c r="M71">
-        <v>0</v>
-      </c>
-      <c r="O71">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="14"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="8"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
+      <c r="C72" t="s">
+        <v>26</v>
+      </c>
+      <c r="D72" t="s">
+        <v>165</v>
+      </c>
+      <c r="E72" t="s">
+        <v>221</v>
+      </c>
+      <c r="F72" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="G72" t="s">
+        <v>168</v>
+      </c>
+      <c r="H72" t="s">
+        <v>169</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
     </row>
     <row r="73" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
-        <v>230</v>
+        <v>79</v>
       </c>
       <c r="B73" t="s">
-        <v>231</v>
+        <v>80</v>
       </c>
       <c r="C73" t="s">
         <v>26</v>
       </c>
       <c r="D73" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E73" t="s">
-        <v>113</v>
+        <v>224</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="G73" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H73" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="I73">
         <v>0</v>
       </c>
-      <c r="J73" t="s">
-        <v>32</v>
-      </c>
       <c r="K73">
         <v>0</v>
       </c>
-      <c r="L73" t="s">
-        <v>32</v>
-      </c>
       <c r="M73">
         <v>0</v>
       </c>
-      <c r="N73" t="s">
-        <v>33</v>
-      </c>
       <c r="O73">
         <v>0</v>
       </c>
-      <c r="P73" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q73" t="s">
+    </row>
+    <row r="74" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="R73" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" t="s">
-        <v>236</v>
-      </c>
-      <c r="B74" t="s">
-        <v>237</v>
-      </c>
-      <c r="C74" t="s">
-        <v>26</v>
-      </c>
-      <c r="D74" t="s">
-        <v>232</v>
-      </c>
-      <c r="E74" t="s">
-        <v>113</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="G74" t="s">
-        <v>234</v>
-      </c>
-      <c r="H74" t="s">
-        <v>162</v>
-      </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74" t="s">
-        <v>32</v>
-      </c>
-      <c r="K74">
-        <v>0</v>
-      </c>
-      <c r="L74" t="s">
-        <v>32</v>
-      </c>
-      <c r="M74">
-        <v>0</v>
-      </c>
-      <c r="N74" t="s">
-        <v>33</v>
-      </c>
-      <c r="O74">
-        <v>0</v>
-      </c>
-      <c r="P74" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q74" t="s">
-        <v>228</v>
-      </c>
-      <c r="R74" t="s">
-        <v>235</v>
-      </c>
+      <c r="B74" s="8"/>
+      <c r="C74" s="8"/>
+      <c r="D74" s="8"/>
+      <c r="E74" s="8"/>
+      <c r="F74" s="14"/>
+      <c r="G74" s="8"/>
+      <c r="H74" s="8"/>
+      <c r="I74" s="8"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
     </row>
     <row r="75" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B75" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C75" t="s">
         <v>26</v>
       </c>
       <c r="D75" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E75" t="s">
         <v>113</v>
       </c>
       <c r="F75" s="12" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G75" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H75" t="s">
         <v>162</v>
@@ -4539,33 +4510,33 @@
         <v>32</v>
       </c>
       <c r="Q75" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R75" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="B76" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="C76" t="s">
         <v>26</v>
       </c>
       <c r="D76" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E76" t="s">
         <v>113</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="G76" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H76" t="s">
         <v>162</v>
@@ -4595,33 +4566,33 @@
         <v>32</v>
       </c>
       <c r="Q76" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R76" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="77" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B77" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="C77" t="s">
         <v>26</v>
       </c>
       <c r="D77" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E77" t="s">
         <v>113</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="G77" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H77" t="s">
         <v>162</v>
@@ -4650,31 +4621,34 @@
       <c r="P77" t="s">
         <v>32</v>
       </c>
+      <c r="Q77" t="s">
+        <v>227</v>
+      </c>
       <c r="R77" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="78" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B78" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C78" t="s">
         <v>26</v>
       </c>
       <c r="D78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E78" t="s">
         <v>113</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="G78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H78" t="s">
         <v>162</v>
@@ -4704,33 +4678,33 @@
         <v>32</v>
       </c>
       <c r="Q78" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="R78" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B79" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C79" t="s">
         <v>26</v>
       </c>
       <c r="D79" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E79" t="s">
         <v>113</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="G79" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H79" t="s">
         <v>162</v>
@@ -4759,119 +4733,140 @@
       <c r="P79" t="s">
         <v>32</v>
       </c>
-      <c r="Q79" t="s">
-        <v>228</v>
-      </c>
       <c r="R79" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="80" spans="1:18" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A80" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B80" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="C80" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="E80" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="F80" s="15" t="s">
-        <v>277</v>
-      </c>
-      <c r="G80" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H80" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I80" s="10">
-        <v>0</v>
-      </c>
-      <c r="J80" s="11"/>
-      <c r="K80" s="10">
-        <v>0</v>
-      </c>
-      <c r="L80" s="11"/>
-      <c r="M80" s="10">
-        <v>0</v>
-      </c>
-      <c r="N80" s="11"/>
-      <c r="O80" s="10">
-        <v>0</v>
-      </c>
-      <c r="P80" s="11"/>
-      <c r="Q80" s="11"/>
-      <c r="R80" s="11"/>
-    </row>
-    <row r="81" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B81" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="C81" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D81" s="10" t="s">
-        <v>283</v>
-      </c>
-      <c r="E81" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="F81" s="15" t="s">
-        <v>278</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I81" s="10">
-        <v>0</v>
-      </c>
-      <c r="J81" s="11"/>
-      <c r="K81" s="10">
-        <v>0</v>
-      </c>
-      <c r="L81" s="11"/>
-      <c r="M81" s="10">
-        <v>0</v>
-      </c>
-      <c r="N81" s="11"/>
-      <c r="O81" s="10">
-        <v>0</v>
-      </c>
-      <c r="P81" s="11"/>
-      <c r="Q81" s="11"/>
-      <c r="R81" s="11"/>
-    </row>
-    <row r="82" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A80" t="s">
+        <v>247</v>
+      </c>
+      <c r="B80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C80" t="s">
+        <v>26</v>
+      </c>
+      <c r="D80" t="s">
+        <v>231</v>
+      </c>
+      <c r="E80" t="s">
+        <v>113</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="G80" t="s">
+        <v>233</v>
+      </c>
+      <c r="H80" t="s">
+        <v>162</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80" t="s">
+        <v>32</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80" t="s">
+        <v>32</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80" t="s">
+        <v>33</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>227</v>
+      </c>
+      <c r="R80" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A81" t="s">
+        <v>250</v>
+      </c>
+      <c r="B81" t="s">
+        <v>251</v>
+      </c>
+      <c r="C81" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" t="s">
+        <v>231</v>
+      </c>
+      <c r="E81" t="s">
+        <v>113</v>
+      </c>
+      <c r="F81" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="G81" t="s">
+        <v>233</v>
+      </c>
+      <c r="H81" t="s">
+        <v>162</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81" t="s">
+        <v>32</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81" t="s">
+        <v>32</v>
+      </c>
+      <c r="M81">
+        <v>0</v>
+      </c>
+      <c r="N81" t="s">
+        <v>33</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>227</v>
+      </c>
+      <c r="R81" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A82" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C82" s="10" t="s">
         <v>26</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F82" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>163</v>
@@ -4903,19 +4898,19 @@
         <v>58</v>
       </c>
       <c r="B83" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="E83" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>273</v>
-      </c>
-      <c r="E83" s="10" t="s">
-        <v>273</v>
-      </c>
       <c r="F83" s="15" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>163</v>
@@ -4942,12 +4937,101 @@
       <c r="Q83" s="11"/>
       <c r="R83" s="11"/>
     </row>
+    <row r="84" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A84" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B84" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D84" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="F84" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I84" s="10">
+        <v>0</v>
+      </c>
+      <c r="J84" s="11"/>
+      <c r="K84" s="10">
+        <v>0</v>
+      </c>
+      <c r="L84" s="11"/>
+      <c r="M84" s="10">
+        <v>0</v>
+      </c>
+      <c r="N84" s="11"/>
+      <c r="O84" s="10">
+        <v>0</v>
+      </c>
+      <c r="P84" s="11"/>
+      <c r="Q84" s="11"/>
+      <c r="R84" s="11"/>
+    </row>
+    <row r="85" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A85" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D85" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F85" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I85" s="10">
+        <v>0</v>
+      </c>
+      <c r="J85" s="11"/>
+      <c r="K85" s="10">
+        <v>0</v>
+      </c>
+      <c r="L85" s="11"/>
+      <c r="M85" s="10">
+        <v>0</v>
+      </c>
+      <c r="N85" s="11"/>
+      <c r="O85" s="10">
+        <v>0</v>
+      </c>
+      <c r="P85" s="11"/>
+      <c r="Q85" s="11"/>
+      <c r="R85" s="11"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R79" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:R85" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <customProperties>
-    <customPr name="BudgetSheetCodeName" r:id="rId1"/>
+    <customPr name="BudgetSheetCodeName" r:id="rId2"/>
   </customProperties>
 </worksheet>
 </file>

--- a/public/Examination/考核应用报表导出模板_202604091814.xlsx
+++ b/public/Examination/考核应用报表导出模板_202604091814.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3991E240-6463-4331-978F-C20FD5FC61CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9453E4F1-E5BA-43E1-95F9-01037E5A5370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11,15 +11,15 @@
     <sheet name="评估组1-定量指标" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'评估组1-定量指标'!$A$2:$R$85</definedName>
-    <definedName name="_xlnm._FilterDatabase">'评估组1-定量指标'!$A$2:$R$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'评估组1-定量指标'!$A$2:$R$86</definedName>
+    <definedName name="_xlnm._FilterDatabase">'评估组1-定量指标'!$A$2:$R$74</definedName>
   </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="819" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="289">
   <si>
     <t>HR备注：</t>
   </si>
@@ -963,6 +963,14 @@
   </si>
   <si>
     <t>达人活跃数</t>
+  </si>
+  <si>
+    <t>王琳</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>自有产品净毛利</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1053,7 +1061,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1095,6 +1103,9 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1372,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R85"/>
+  <dimension ref="A1:R86"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="4" max="4" width="51.625" customWidth="1"/>
@@ -1459,29 +1470,17 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>25</v>
+      <c r="B3" s="17" t="s">
+        <v>287</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G3" t="s">
-        <v>30</v>
-      </c>
-      <c r="H3" t="s">
-        <v>31</v>
+      <c r="D3" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>288</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1509,123 +1508,123 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="6" t="s">
+      <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>33</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F5" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" s="6" t="s">
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5" t="s">
-        <v>32</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>33</v>
-      </c>
       <c r="O5">
         <v>0</v>
       </c>
-      <c r="P5" t="s">
+      <c r="P5" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>262</v>
+      <c r="D6" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>273</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
         <v>30</v>
@@ -1659,329 +1658,329 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="6" t="s">
+      <c r="A7" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" t="s">
         <v>26</v>
       </c>
       <c r="D7" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="G7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H7" t="s">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7" t="s">
+        <v>32</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>33</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A8" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E8" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F8" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7" t="s">
-        <v>32</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7" s="6" t="s">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8" t="s">
+        <v>32</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" t="s">
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A9" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C8" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G9" t="s">
         <v>30</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H9" t="s">
         <v>31</v>
       </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>32</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8" t="s">
-        <v>32</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8" t="s">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>32</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9" t="s">
+        <v>32</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
         <v>33</v>
       </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="6" t="s">
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A10" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="9" t="s">
+      <c r="C10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F10" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H10" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9" s="6" t="s">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" t="s">
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A11" t="s">
         <v>54</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B11" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="6" t="s">
+      <c r="C11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F11" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G11" t="s">
         <v>30</v>
       </c>
-      <c r="H10" t="s">
+      <c r="H11" t="s">
         <v>31</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10" t="s">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>32</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11" t="s">
+        <v>32</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
         <v>33</v>
       </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="6" t="s">
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="6" t="s">
+      <c r="C12" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F12" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H12" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" s="6" t="s">
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" t="s">
-        <v>58</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12" t="s">
-        <v>62</v>
-      </c>
-      <c r="H12" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>32</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12" t="s">
-        <v>32</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>33</v>
-      </c>
       <c r="O12">
         <v>0</v>
       </c>
-      <c r="P12" t="s">
+      <c r="P12" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>65</v>
+        <v>58</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>253</v>
       </c>
       <c r="C13" t="s">
         <v>26</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>28</v>
+        <v>254</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -2009,111 +2008,111 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="6" t="s">
+      <c r="A14" t="s">
         <v>64</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" t="s">
         <v>26</v>
       </c>
       <c r="D14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" t="s">
+        <v>31</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>32</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>32</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>33</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F15" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H15" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14" s="6" t="s">
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" t="s">
-        <v>68</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="G15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>32</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>33</v>
-      </c>
       <c r="O15">
         <v>0</v>
       </c>
-      <c r="P15" t="s">
+      <c r="P15" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
         <v>26</v>
@@ -2125,7 +2124,7 @@
         <v>28</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
         <v>30</v>
@@ -2159,229 +2158,229 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="6" t="s">
+      <c r="A17" t="s">
         <v>71</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" t="s">
         <v>26</v>
       </c>
       <c r="D17" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G17" t="s">
+        <v>30</v>
+      </c>
+      <c r="H17" t="s">
+        <v>31</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17" t="s">
+        <v>32</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>33</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A18" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F18" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H18" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K17">
-        <v>0</v>
-      </c>
-      <c r="L17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-      <c r="N17" s="6" t="s">
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O17">
-        <v>0</v>
-      </c>
-      <c r="P17" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" t="s">
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" t="s">
         <v>75</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B19" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C18" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="C19" t="s">
+        <v>26</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F19" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G19" t="s">
         <v>30</v>
       </c>
-      <c r="H18" t="s">
+      <c r="H19" t="s">
         <v>31</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18">
-        <v>0</v>
-      </c>
-      <c r="L18" t="s">
-        <v>32</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-      <c r="N18" t="s">
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>32</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19" t="s">
         <v>33</v>
       </c>
-      <c r="O18">
-        <v>0</v>
-      </c>
-      <c r="P18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="6" t="s">
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B20" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="C19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="C20" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F20" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H20" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-      <c r="N19" s="6" t="s">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="O19">
-        <v>0</v>
-      </c>
-      <c r="P19" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="G20" t="s">
-        <v>52</v>
-      </c>
-      <c r="H20" t="s">
-        <v>53</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
-      <c r="K20">
-        <v>0</v>
-      </c>
-      <c r="L20" t="s">
-        <v>32</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20" t="s">
-        <v>33</v>
-      </c>
       <c r="O20">
         <v>0</v>
       </c>
-      <c r="P20" t="s">
+      <c r="P20" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>82</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>83</v>
+        <v>79</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>80</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -2412,26 +2411,26 @@
       <c r="A22" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>83</v>
       </c>
       <c r="C22" t="s">
         <v>26</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2460,28 +2459,28 @@
     </row>
     <row r="23" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>88</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>89</v>
+        <v>82</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>83</v>
       </c>
       <c r="C23" t="s">
         <v>26</v>
       </c>
-      <c r="D23" t="s">
-        <v>27</v>
-      </c>
-      <c r="E23" t="s">
-        <v>84</v>
+      <c r="D23" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>86</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -2510,10 +2509,10 @@
     </row>
     <row r="24" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C24" t="s">
         <v>26</v>
@@ -2525,7 +2524,7 @@
         <v>84</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G24" t="s">
         <v>30</v>
@@ -2560,10 +2559,10 @@
     </row>
     <row r="25" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
         <v>26</v>
@@ -2575,7 +2574,7 @@
         <v>84</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s">
         <v>30</v>
@@ -2610,25 +2609,28 @@
     </row>
     <row r="26" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B26" t="s">
-        <v>98</v>
+        <v>94</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>95</v>
       </c>
       <c r="C26" t="s">
         <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
       <c r="E26" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G26" t="s">
-        <v>102</v>
+        <v>30</v>
+      </c>
+      <c r="H26" t="s">
+        <v>31</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -2638,6 +2640,9 @@
       </c>
       <c r="K26">
         <v>0</v>
+      </c>
+      <c r="L26" t="s">
+        <v>32</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -2663,16 +2668,16 @@
         <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E27" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G27" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -2698,25 +2703,25 @@
     </row>
     <row r="28" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B28" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="C28" t="s">
         <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E28" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -2751,16 +2756,16 @@
         <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E29" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G29" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -2786,25 +2791,25 @@
     </row>
     <row r="30" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C30" t="s">
         <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E30" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="G30" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -2839,16 +2844,16 @@
         <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E31" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G31" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -2873,57 +2878,63 @@
       </c>
     </row>
     <row r="32" spans="1:16" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="8" t="s">
+      <c r="A32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E32" t="s">
+        <v>115</v>
+      </c>
+      <c r="F32" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G32" t="s">
+        <v>106</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>32</v>
+      </c>
+      <c r="K32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32" t="s">
+        <v>33</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="8"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="8"/>
-      <c r="H32" s="8"/>
-      <c r="I32" s="8"/>
-      <c r="J32" s="8"/>
-      <c r="K32" s="8"/>
-    </row>
-    <row r="33" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" t="s">
-        <v>25</v>
-      </c>
-      <c r="C33" t="s">
-        <v>26</v>
-      </c>
-      <c r="D33" t="s">
-        <v>118</v>
-      </c>
-      <c r="E33" t="s">
-        <v>119</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="G33" t="s">
-        <v>121</v>
-      </c>
-      <c r="H33" t="s">
-        <v>122</v>
-      </c>
-      <c r="I33">
-        <v>0</v>
-      </c>
-      <c r="K33">
-        <v>0</v>
-      </c>
-      <c r="M33">
-        <v>0</v>
-      </c>
-      <c r="O33">
-        <v>0</v>
-      </c>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
     </row>
     <row r="34" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
@@ -2936,19 +2947,19 @@
         <v>26</v>
       </c>
       <c r="D34" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E34" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="G34" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H34" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -2965,28 +2976,28 @@
     </row>
     <row r="35" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B35" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C35" t="s">
         <v>26</v>
       </c>
       <c r="D35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G35" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="H35" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -3012,13 +3023,13 @@
         <v>26</v>
       </c>
       <c r="D36" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E36" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G36" t="s">
         <v>129</v>
@@ -3050,19 +3061,19 @@
         <v>26</v>
       </c>
       <c r="D37" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="E37" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H37" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -3088,19 +3099,19 @@
         <v>26</v>
       </c>
       <c r="D38" t="s">
-        <v>266</v>
+        <v>134</v>
       </c>
       <c r="E38" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="G38" t="s">
         <v>125</v>
       </c>
       <c r="H38" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -3117,28 +3128,28 @@
     </row>
     <row r="39" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="C39" t="s">
         <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>119</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>144</v>
+        <v>266</v>
+      </c>
+      <c r="E39" t="s">
+        <v>138</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G39" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="H39" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -3164,19 +3175,19 @@
         <v>26</v>
       </c>
       <c r="D40" t="s">
-        <v>146</v>
-      </c>
-      <c r="E40" t="s">
-        <v>147</v>
+        <v>119</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="G40" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H40" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -3193,28 +3204,28 @@
     </row>
     <row r="41" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="B41" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C41" t="s">
         <v>26</v>
       </c>
       <c r="D41" t="s">
-        <v>49</v>
+        <v>146</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="G41" t="s">
-        <v>52</v>
+        <v>121</v>
       </c>
       <c r="H41" t="s">
-        <v>53</v>
+        <v>149</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -3231,28 +3242,28 @@
     </row>
     <row r="42" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="C42" t="s">
         <v>26</v>
       </c>
       <c r="D42" t="s">
-        <v>152</v>
+        <v>49</v>
       </c>
       <c r="E42" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>52</v>
       </c>
       <c r="H42" t="s">
-        <v>156</v>
+        <v>53</v>
       </c>
       <c r="I42">
         <v>0</v>
@@ -3269,28 +3280,28 @@
     </row>
     <row r="43" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
-        <v>157</v>
+        <v>54</v>
       </c>
       <c r="B43" t="s">
-        <v>158</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
         <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="E43" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="G43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H43" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -3307,28 +3318,28 @@
     </row>
     <row r="44" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
-        <v>58</v>
+        <v>157</v>
       </c>
       <c r="B44" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="C44" t="s">
         <v>26</v>
       </c>
       <c r="D44" t="s">
-        <v>265</v>
+        <v>159</v>
       </c>
       <c r="E44" t="s">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>280</v>
+        <v>161</v>
       </c>
       <c r="G44" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H44" t="s">
-        <v>63</v>
+        <v>162</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -3345,28 +3356,28 @@
     </row>
     <row r="45" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
-        <v>164</v>
+        <v>58</v>
       </c>
       <c r="B45" t="s">
-        <v>284</v>
+        <v>59</v>
       </c>
       <c r="C45" t="s">
         <v>26</v>
       </c>
       <c r="D45" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="E45" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>167</v>
+        <v>280</v>
       </c>
       <c r="G45" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H45" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="I45">
         <v>0</v>
@@ -3392,10 +3403,10 @@
         <v>26</v>
       </c>
       <c r="D46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E46" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F46" s="12" t="s">
         <v>167</v>
@@ -3430,10 +3441,10 @@
         <v>26</v>
       </c>
       <c r="D47" t="s">
-        <v>165</v>
+        <v>286</v>
       </c>
       <c r="E47" t="s">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>167</v>
@@ -3459,10 +3470,10 @@
     </row>
     <row r="48" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="B48" t="s">
-        <v>171</v>
+        <v>284</v>
       </c>
       <c r="C48" t="s">
         <v>26</v>
@@ -3474,7 +3485,7 @@
         <v>166</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G48" t="s">
         <v>168</v>
@@ -3497,10 +3508,10 @@
     </row>
     <row r="49" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
-        <v>255</v>
+        <v>171</v>
       </c>
       <c r="C49" t="s">
         <v>26</v>
@@ -3509,10 +3520,10 @@
         <v>165</v>
       </c>
       <c r="E49" t="s">
-        <v>256</v>
+        <v>166</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G49" t="s">
         <v>168</v>
@@ -3535,28 +3546,28 @@
     </row>
     <row r="50" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
-        <v>65</v>
+        <v>255</v>
       </c>
       <c r="C50" t="s">
         <v>26</v>
       </c>
       <c r="D50" t="s">
-        <v>141</v>
+        <v>165</v>
       </c>
       <c r="E50" t="s">
-        <v>141</v>
+        <v>256</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G50" t="s">
-        <v>121</v>
+        <v>168</v>
       </c>
       <c r="H50" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -3582,19 +3593,19 @@
         <v>26</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E51" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G51" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H51" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -3611,28 +3622,28 @@
     </row>
     <row r="52" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>64</v>
       </c>
       <c r="B52" t="s">
-        <v>179</v>
+        <v>65</v>
       </c>
       <c r="C52" t="s">
         <v>26</v>
       </c>
       <c r="D52" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="E52" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="G52" t="s">
-        <v>182</v>
+        <v>125</v>
       </c>
       <c r="H52" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -3658,13 +3669,13 @@
         <v>26</v>
       </c>
       <c r="D53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E53" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="G53" t="s">
         <v>182</v>
@@ -3696,16 +3707,16 @@
         <v>26</v>
       </c>
       <c r="D54" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="E54" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G54" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="H54" t="s">
         <v>183</v>
@@ -3734,19 +3745,19 @@
         <v>26</v>
       </c>
       <c r="D55" t="s">
-        <v>267</v>
+        <v>186</v>
       </c>
       <c r="E55" t="s">
-        <v>267</v>
+        <v>186</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>275</v>
+        <v>187</v>
       </c>
       <c r="G55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H55" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="I55">
         <v>0</v>
@@ -3763,28 +3774,28 @@
     </row>
     <row r="56" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
-        <v>91</v>
+        <v>178</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>179</v>
       </c>
       <c r="C56" t="s">
         <v>26</v>
       </c>
       <c r="D56" t="s">
-        <v>86</v>
+        <v>267</v>
       </c>
       <c r="E56" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>191</v>
+        <v>275</v>
       </c>
       <c r="G56" t="s">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="H56" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -3810,19 +3821,19 @@
         <v>26</v>
       </c>
       <c r="D57" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E57" t="s">
-        <v>144</v>
+        <v>261</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G57" t="s">
         <v>142</v>
       </c>
       <c r="H57" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="I57">
         <v>0</v>
@@ -3848,19 +3859,19 @@
         <v>26</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="E58" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G58" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H58" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -3877,28 +3888,28 @@
     </row>
     <row r="59" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
-        <v>195</v>
+        <v>91</v>
       </c>
       <c r="B59" t="s">
-        <v>257</v>
+        <v>92</v>
       </c>
       <c r="C59" t="s">
         <v>26</v>
       </c>
       <c r="D59" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E59" t="s">
-        <v>256</v>
+        <v>147</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G59" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="H59" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -3915,28 +3926,28 @@
     </row>
     <row r="60" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
-        <v>198</v>
+        <v>257</v>
       </c>
       <c r="C60" t="s">
         <v>26</v>
       </c>
       <c r="D60" t="s">
-        <v>199</v>
+        <v>165</v>
       </c>
       <c r="E60" t="s">
-        <v>199</v>
+        <v>256</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="G60" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="H60" t="s">
-        <v>63</v>
+        <v>169</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3953,28 +3964,28 @@
     </row>
     <row r="61" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B61" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="C61" t="s">
         <v>26</v>
       </c>
       <c r="D61" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="E61" t="s">
-        <v>166</v>
+        <v>199</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G61" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="H61" t="s">
-        <v>169</v>
+        <v>63</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3991,10 +4002,10 @@
     </row>
     <row r="62" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B62" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C62" t="s">
         <v>26</v>
@@ -4003,10 +4014,10 @@
         <v>165</v>
       </c>
       <c r="E62" t="s">
-        <v>256</v>
+        <v>166</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G62" t="s">
         <v>168</v>
@@ -4029,28 +4040,28 @@
     </row>
     <row r="63" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
-        <v>68</v>
+        <v>204</v>
       </c>
       <c r="B63" t="s">
-        <v>258</v>
+        <v>205</v>
       </c>
       <c r="C63" t="s">
         <v>26</v>
       </c>
       <c r="D63" t="s">
-        <v>207</v>
+        <v>165</v>
       </c>
       <c r="E63" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F63" s="12" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G63" t="s">
-        <v>209</v>
+        <v>168</v>
       </c>
       <c r="H63" t="s">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -4076,19 +4087,19 @@
         <v>26</v>
       </c>
       <c r="D64" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E64" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F64" s="12" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="G64" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="H64" t="s">
-        <v>137</v>
+        <v>210</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -4105,28 +4116,28 @@
     </row>
     <row r="65" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B65" t="s">
-        <v>72</v>
+        <v>258</v>
       </c>
       <c r="C65" t="s">
         <v>26</v>
       </c>
       <c r="D65" t="s">
-        <v>119</v>
+        <v>211</v>
       </c>
       <c r="E65" t="s">
-        <v>141</v>
+        <v>260</v>
       </c>
       <c r="F65" s="12" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G65" t="s">
-        <v>142</v>
+        <v>213</v>
       </c>
       <c r="H65" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="I65">
         <v>0</v>
@@ -4152,19 +4163,19 @@
         <v>26</v>
       </c>
       <c r="D66" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="E66" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F66" s="12" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G66" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="H66" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -4181,28 +4192,28 @@
     </row>
     <row r="67" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
         <v>26</v>
       </c>
       <c r="D67" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E67" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G67" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H67" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="I67">
         <v>0</v>
@@ -4228,19 +4239,19 @@
         <v>26</v>
       </c>
       <c r="D68" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E68" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G68" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="H68" t="s">
-        <v>137</v>
+        <v>176</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -4257,28 +4268,28 @@
     </row>
     <row r="69" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="C69" t="s">
         <v>26</v>
       </c>
       <c r="D69" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="E69" t="s">
-        <v>86</v>
+        <v>147</v>
       </c>
       <c r="F69" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G69" t="s">
-        <v>142</v>
+        <v>125</v>
       </c>
       <c r="H69" t="s">
-        <v>192</v>
+        <v>137</v>
       </c>
       <c r="I69">
         <v>0</v>
@@ -4304,19 +4315,19 @@
         <v>26</v>
       </c>
       <c r="D70" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="E70" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="F70" s="12" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G70" t="s">
         <v>142</v>
       </c>
       <c r="H70" t="s">
-        <v>143</v>
+        <v>192</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -4342,19 +4353,19 @@
         <v>26</v>
       </c>
       <c r="D71" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="E71" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F71" s="12" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G71" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="H71" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="I71">
         <v>0</v>
@@ -4371,28 +4382,28 @@
     </row>
     <row r="72" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C72" t="s">
         <v>26</v>
       </c>
       <c r="D72" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="E72" t="s">
-        <v>221</v>
+        <v>147</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G72" t="s">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="H72" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -4418,110 +4429,92 @@
         <v>26</v>
       </c>
       <c r="D73" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" t="s">
+        <v>221</v>
+      </c>
+      <c r="F73" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="G73" t="s">
+        <v>168</v>
+      </c>
+      <c r="H73" t="s">
+        <v>169</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A74" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" t="s">
+        <v>80</v>
+      </c>
+      <c r="C74" t="s">
+        <v>26</v>
+      </c>
+      <c r="D74" t="s">
         <v>223</v>
       </c>
-      <c r="E73" t="s">
+      <c r="E74" t="s">
         <v>224</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F74" s="12" t="s">
         <v>225</v>
       </c>
-      <c r="G73" t="s">
+      <c r="G74" t="s">
         <v>226</v>
       </c>
-      <c r="H73" t="s">
+      <c r="H74" t="s">
         <v>227</v>
       </c>
-      <c r="I73">
-        <v>0</v>
-      </c>
-      <c r="K73">
-        <v>0</v>
-      </c>
-      <c r="M73">
-        <v>0</v>
-      </c>
-      <c r="O73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="8" t="s">
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="14"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="8"/>
-      <c r="J74" s="8"/>
-      <c r="K74" s="8"/>
-    </row>
-    <row r="75" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" t="s">
-        <v>229</v>
-      </c>
-      <c r="B75" t="s">
-        <v>230</v>
-      </c>
-      <c r="C75" t="s">
-        <v>26</v>
-      </c>
-      <c r="D75" t="s">
-        <v>231</v>
-      </c>
-      <c r="E75" t="s">
-        <v>113</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="G75" t="s">
-        <v>233</v>
-      </c>
-      <c r="H75" t="s">
-        <v>162</v>
-      </c>
-      <c r="I75">
-        <v>0</v>
-      </c>
-      <c r="J75" t="s">
-        <v>32</v>
-      </c>
-      <c r="K75">
-        <v>0</v>
-      </c>
-      <c r="L75" t="s">
-        <v>32</v>
-      </c>
-      <c r="M75">
-        <v>0</v>
-      </c>
-      <c r="N75" t="s">
-        <v>33</v>
-      </c>
-      <c r="O75">
-        <v>0</v>
-      </c>
-      <c r="P75" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q75" t="s">
-        <v>227</v>
-      </c>
-      <c r="R75" t="s">
-        <v>234</v>
-      </c>
+      <c r="B75" s="8"/>
+      <c r="C75" s="8"/>
+      <c r="D75" s="8"/>
+      <c r="E75" s="8"/>
+      <c r="F75" s="14"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="8"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
     </row>
     <row r="76" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B76" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C76" t="s">
         <v>26</v>
@@ -4533,7 +4526,7 @@
         <v>113</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G76" t="s">
         <v>233</v>
@@ -4574,10 +4567,10 @@
     </row>
     <row r="77" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B77" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C77" t="s">
         <v>26</v>
@@ -4589,7 +4582,7 @@
         <v>113</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="G77" t="s">
         <v>233</v>
@@ -4630,10 +4623,10 @@
     </row>
     <row r="78" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B78" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C78" t="s">
         <v>26</v>
@@ -4645,7 +4638,7 @@
         <v>113</v>
       </c>
       <c r="F78" s="12" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="G78" t="s">
         <v>233</v>
@@ -4686,10 +4679,10 @@
     </row>
     <row r="79" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B79" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C79" t="s">
         <v>26</v>
@@ -4701,7 +4694,7 @@
         <v>113</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G79" t="s">
         <v>233</v>
@@ -4733,16 +4726,19 @@
       <c r="P79" t="s">
         <v>32</v>
       </c>
+      <c r="Q79" t="s">
+        <v>227</v>
+      </c>
       <c r="R79" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="B80" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C80" t="s">
         <v>26</v>
@@ -4754,7 +4750,7 @@
         <v>113</v>
       </c>
       <c r="F80" s="12" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G80" t="s">
         <v>233</v>
@@ -4786,19 +4782,16 @@
       <c r="P80" t="s">
         <v>32</v>
       </c>
-      <c r="Q80" t="s">
-        <v>227</v>
-      </c>
       <c r="R80" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B81" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C81" t="s">
         <v>26</v>
@@ -4810,7 +4803,7 @@
         <v>113</v>
       </c>
       <c r="F81" s="12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G81" t="s">
         <v>233</v>
@@ -4849,51 +4842,63 @@
         <v>234</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A82" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B82" s="10" t="s">
-        <v>269</v>
-      </c>
-      <c r="C82" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D82" s="10" t="s">
-        <v>281</v>
-      </c>
-      <c r="E82" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="F82" s="15" t="s">
-        <v>276</v>
-      </c>
-      <c r="G82" s="10" t="s">
-        <v>163</v>
-      </c>
-      <c r="H82" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="I82" s="10">
-        <v>0</v>
-      </c>
-      <c r="J82" s="11"/>
-      <c r="K82" s="10">
-        <v>0</v>
-      </c>
-      <c r="L82" s="11"/>
-      <c r="M82" s="10">
-        <v>0</v>
-      </c>
-      <c r="N82" s="11"/>
-      <c r="O82" s="10">
-        <v>0</v>
-      </c>
-      <c r="P82" s="11"/>
-      <c r="Q82" s="11"/>
-      <c r="R82" s="11"/>
-    </row>
-    <row r="83" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A82" t="s">
+        <v>250</v>
+      </c>
+      <c r="B82" t="s">
+        <v>251</v>
+      </c>
+      <c r="C82" t="s">
+        <v>26</v>
+      </c>
+      <c r="D82" t="s">
+        <v>231</v>
+      </c>
+      <c r="E82" t="s">
+        <v>113</v>
+      </c>
+      <c r="F82" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="G82" t="s">
+        <v>233</v>
+      </c>
+      <c r="H82" t="s">
+        <v>162</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82" t="s">
+        <v>32</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82" t="s">
+        <v>32</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82" t="s">
+        <v>33</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>227</v>
+      </c>
+      <c r="R82" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A83" s="10" t="s">
         <v>58</v>
       </c>
@@ -4904,13 +4909,13 @@
         <v>26</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F83" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G83" s="10" t="s">
         <v>163</v>
@@ -4948,13 +4953,13 @@
         <v>26</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F84" s="15" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="G84" s="10" t="s">
         <v>163</v>
@@ -4992,13 +4997,13 @@
         <v>26</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="E85" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F85" s="15" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G85" s="10" t="s">
         <v>163</v>
@@ -5025,8 +5030,52 @@
       <c r="Q85" s="11"/>
       <c r="R85" s="11"/>
     </row>
+    <row r="86" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A86" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B86" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D86" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F86" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="I86" s="10">
+        <v>0</v>
+      </c>
+      <c r="J86" s="11"/>
+      <c r="K86" s="10">
+        <v>0</v>
+      </c>
+      <c r="L86" s="11"/>
+      <c r="M86" s="10">
+        <v>0</v>
+      </c>
+      <c r="N86" s="11"/>
+      <c r="O86" s="10">
+        <v>0</v>
+      </c>
+      <c r="P86" s="11"/>
+      <c r="Q86" s="11"/>
+      <c r="R86" s="11"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:R85" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A2:R86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/public/Examination/考核应用报表导出模板_202604091814.xlsx
+++ b/public/Examination/考核应用报表导出模板_202604091814.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9453E4F1-E5BA-43E1-95F9-01037E5A5370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4C5EE4-4FBD-4D28-B8E2-B06ACB40435D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1061,7 +1061,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1084,9 +1084,6 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1098,9 +1095,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1108,6 +1102,9 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1388,7 +1385,7 @@
   <cols>
     <col min="4" max="4" width="51.625" customWidth="1"/>
     <col min="5" max="5" width="32.375" customWidth="1"/>
-    <col min="6" max="6" width="34.875" style="12" customWidth="1"/>
+    <col min="6" max="6" width="34.875" style="11" customWidth="1"/>
     <col min="9" max="9" width="56.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1470,16 +1467,16 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="15" t="s">
         <v>287</v>
       </c>
       <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="8" t="s">
         <v>288</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>288</v>
       </c>
       <c r="I3">
@@ -1523,7 +1520,7 @@
       <c r="E4" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>29</v>
       </c>
       <c r="G4" t="s">
@@ -1573,7 +1570,7 @@
       <c r="E5" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>35</v>
       </c>
       <c r="G5" s="6" t="s">
@@ -1623,7 +1620,7 @@
       <c r="E6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>40</v>
       </c>
       <c r="G6" t="s">
@@ -1667,13 +1664,13 @@
       <c r="C7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>273</v>
       </c>
       <c r="G7" t="s">
@@ -1717,13 +1714,13 @@
       <c r="C8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="14" t="s">
         <v>274</v>
       </c>
       <c r="G8" s="6" t="s">
@@ -1773,7 +1770,7 @@
       <c r="E9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="11" t="s">
         <v>48</v>
       </c>
       <c r="G9" t="s">
@@ -1817,13 +1814,13 @@
       <c r="C10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="8" t="s">
         <v>264</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="12" t="s">
         <v>51</v>
       </c>
       <c r="G10" s="6" t="s">
@@ -1873,7 +1870,7 @@
       <c r="E11" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="11" t="s">
         <v>56</v>
       </c>
       <c r="G11" t="s">
@@ -1923,7 +1920,7 @@
       <c r="E12" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="12" t="s">
         <v>57</v>
       </c>
       <c r="G12" s="6" t="s">
@@ -1973,7 +1970,7 @@
       <c r="E13" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="11" t="s">
         <v>61</v>
       </c>
       <c r="G13" t="s">
@@ -2023,7 +2020,7 @@
       <c r="E14" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="12" t="s">
+      <c r="F14" s="11" t="s">
         <v>66</v>
       </c>
       <c r="G14" t="s">
@@ -2073,7 +2070,7 @@
       <c r="E15" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="12" t="s">
         <v>67</v>
       </c>
       <c r="G15" s="6" t="s">
@@ -2123,7 +2120,7 @@
       <c r="E16" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="11" t="s">
         <v>70</v>
       </c>
       <c r="G16" t="s">
@@ -2173,7 +2170,7 @@
       <c r="E17" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="11" t="s">
         <v>73</v>
       </c>
       <c r="G17" t="s">
@@ -2223,7 +2220,7 @@
       <c r="E18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="12" t="s">
         <v>74</v>
       </c>
       <c r="G18" s="6" t="s">
@@ -2273,7 +2270,7 @@
       <c r="E19" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G19" t="s">
@@ -2323,7 +2320,7 @@
       <c r="E20" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="13" t="s">
+      <c r="F20" s="12" t="s">
         <v>78</v>
       </c>
       <c r="G20" s="6" t="s">
@@ -2373,7 +2370,7 @@
       <c r="E21" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="11" t="s">
         <v>81</v>
       </c>
       <c r="G21" t="s">
@@ -2423,7 +2420,7 @@
       <c r="E22" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="11" t="s">
         <v>85</v>
       </c>
       <c r="G22" t="s">
@@ -2473,7 +2470,7 @@
       <c r="E23" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="11" t="s">
         <v>87</v>
       </c>
       <c r="G23" t="s">
@@ -2523,7 +2520,7 @@
       <c r="E24" t="s">
         <v>84</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="11" t="s">
         <v>90</v>
       </c>
       <c r="G24" t="s">
@@ -2573,7 +2570,7 @@
       <c r="E25" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="11" t="s">
         <v>93</v>
       </c>
       <c r="G25" t="s">
@@ -2623,7 +2620,7 @@
       <c r="E26" t="s">
         <v>84</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="11" t="s">
         <v>96</v>
       </c>
       <c r="G26" t="s">
@@ -2673,7 +2670,7 @@
       <c r="E27" t="s">
         <v>100</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="11" t="s">
         <v>101</v>
       </c>
       <c r="G27" t="s">
@@ -2717,7 +2714,7 @@
       <c r="E28" t="s">
         <v>104</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="11" t="s">
         <v>105</v>
       </c>
       <c r="G28" t="s">
@@ -2761,7 +2758,7 @@
       <c r="E29" t="s">
         <v>100</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="11" t="s">
         <v>109</v>
       </c>
       <c r="G29" t="s">
@@ -2805,7 +2802,7 @@
       <c r="E30" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="11" t="s">
         <v>110</v>
       </c>
       <c r="G30" t="s">
@@ -2849,7 +2846,7 @@
       <c r="E31" t="s">
         <v>113</v>
       </c>
-      <c r="F31" s="12" t="s">
+      <c r="F31" s="11" t="s">
         <v>114</v>
       </c>
       <c r="G31" t="s">
@@ -2893,7 +2890,7 @@
       <c r="E32" t="s">
         <v>115</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="11" t="s">
         <v>116</v>
       </c>
       <c r="G32" t="s">
@@ -2921,20 +2918,20 @@
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="8" t="s">
+    <row r="33" spans="1:15" s="16" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
     </row>
     <row r="34" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
@@ -2952,7 +2949,7 @@
       <c r="E34" t="s">
         <v>119</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="11" t="s">
         <v>120</v>
       </c>
       <c r="G34" t="s">
@@ -2990,7 +2987,7 @@
       <c r="E35" t="s">
         <v>123</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="11" t="s">
         <v>124</v>
       </c>
       <c r="G35" t="s">
@@ -3028,7 +3025,7 @@
       <c r="E36" t="s">
         <v>127</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="11" t="s">
         <v>128</v>
       </c>
       <c r="G36" t="s">
@@ -3066,7 +3063,7 @@
       <c r="E37" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="11" t="s">
         <v>133</v>
       </c>
       <c r="G37" t="s">
@@ -3104,7 +3101,7 @@
       <c r="E38" t="s">
         <v>135</v>
       </c>
-      <c r="F38" s="12" t="s">
+      <c r="F38" s="11" t="s">
         <v>136</v>
       </c>
       <c r="G38" t="s">
@@ -3142,7 +3139,7 @@
       <c r="E39" t="s">
         <v>138</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F39" s="11" t="s">
         <v>139</v>
       </c>
       <c r="G39" t="s">
@@ -3180,7 +3177,7 @@
       <c r="E40" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="F40" s="12" t="s">
+      <c r="F40" s="11" t="s">
         <v>145</v>
       </c>
       <c r="G40" t="s">
@@ -3218,7 +3215,7 @@
       <c r="E41" t="s">
         <v>147</v>
       </c>
-      <c r="F41" s="12" t="s">
+      <c r="F41" s="11" t="s">
         <v>148</v>
       </c>
       <c r="G41" t="s">
@@ -3256,7 +3253,7 @@
       <c r="E42" t="s">
         <v>150</v>
       </c>
-      <c r="F42" s="12" t="s">
+      <c r="F42" s="11" t="s">
         <v>151</v>
       </c>
       <c r="G42" t="s">
@@ -3294,7 +3291,7 @@
       <c r="E43" t="s">
         <v>153</v>
       </c>
-      <c r="F43" s="12" t="s">
+      <c r="F43" s="11" t="s">
         <v>154</v>
       </c>
       <c r="G43" t="s">
@@ -3332,7 +3329,7 @@
       <c r="E44" t="s">
         <v>160</v>
       </c>
-      <c r="F44" s="12" t="s">
+      <c r="F44" s="11" t="s">
         <v>161</v>
       </c>
       <c r="G44" t="s">
@@ -3370,7 +3367,7 @@
       <c r="E45" t="s">
         <v>265</v>
       </c>
-      <c r="F45" s="12" t="s">
+      <c r="F45" s="11" t="s">
         <v>280</v>
       </c>
       <c r="G45" t="s">
@@ -3408,7 +3405,7 @@
       <c r="E46" t="s">
         <v>285</v>
       </c>
-      <c r="F46" s="12" t="s">
+      <c r="F46" s="11" t="s">
         <v>167</v>
       </c>
       <c r="G46" t="s">
@@ -3446,7 +3443,7 @@
       <c r="E47" t="s">
         <v>286</v>
       </c>
-      <c r="F47" s="12" t="s">
+      <c r="F47" s="11" t="s">
         <v>167</v>
       </c>
       <c r="G47" t="s">
@@ -3484,7 +3481,7 @@
       <c r="E48" t="s">
         <v>166</v>
       </c>
-      <c r="F48" s="12" t="s">
+      <c r="F48" s="11" t="s">
         <v>167</v>
       </c>
       <c r="G48" t="s">
@@ -3522,7 +3519,7 @@
       <c r="E49" t="s">
         <v>166</v>
       </c>
-      <c r="F49" s="12" t="s">
+      <c r="F49" s="11" t="s">
         <v>172</v>
       </c>
       <c r="G49" t="s">
@@ -3560,7 +3557,7 @@
       <c r="E50" t="s">
         <v>256</v>
       </c>
-      <c r="F50" s="12" t="s">
+      <c r="F50" s="11" t="s">
         <v>174</v>
       </c>
       <c r="G50" t="s">
@@ -3598,7 +3595,7 @@
       <c r="E51" t="s">
         <v>141</v>
       </c>
-      <c r="F51" s="12" t="s">
+      <c r="F51" s="11" t="s">
         <v>175</v>
       </c>
       <c r="G51" t="s">
@@ -3636,7 +3633,7 @@
       <c r="E52" t="s">
         <v>147</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="F52" s="11" t="s">
         <v>177</v>
       </c>
       <c r="G52" t="s">
@@ -3674,7 +3671,7 @@
       <c r="E53" t="s">
         <v>180</v>
       </c>
-      <c r="F53" s="12" t="s">
+      <c r="F53" s="11" t="s">
         <v>181</v>
       </c>
       <c r="G53" t="s">
@@ -3712,7 +3709,7 @@
       <c r="E54" t="s">
         <v>184</v>
       </c>
-      <c r="F54" s="12" t="s">
+      <c r="F54" s="11" t="s">
         <v>185</v>
       </c>
       <c r="G54" t="s">
@@ -3750,7 +3747,7 @@
       <c r="E55" t="s">
         <v>186</v>
       </c>
-      <c r="F55" s="12" t="s">
+      <c r="F55" s="11" t="s">
         <v>187</v>
       </c>
       <c r="G55" t="s">
@@ -3788,7 +3785,7 @@
       <c r="E56" t="s">
         <v>267</v>
       </c>
-      <c r="F56" s="12" t="s">
+      <c r="F56" s="11" t="s">
         <v>275</v>
       </c>
       <c r="G56" t="s">
@@ -3826,7 +3823,7 @@
       <c r="E57" t="s">
         <v>261</v>
       </c>
-      <c r="F57" s="12" t="s">
+      <c r="F57" s="11" t="s">
         <v>191</v>
       </c>
       <c r="G57" t="s">
@@ -3864,7 +3861,7 @@
       <c r="E58" t="s">
         <v>144</v>
       </c>
-      <c r="F58" s="12" t="s">
+      <c r="F58" s="11" t="s">
         <v>193</v>
       </c>
       <c r="G58" t="s">
@@ -3902,7 +3899,7 @@
       <c r="E59" t="s">
         <v>147</v>
       </c>
-      <c r="F59" s="12" t="s">
+      <c r="F59" s="11" t="s">
         <v>194</v>
       </c>
       <c r="G59" t="s">
@@ -3940,7 +3937,7 @@
       <c r="E60" t="s">
         <v>256</v>
       </c>
-      <c r="F60" s="12" t="s">
+      <c r="F60" s="11" t="s">
         <v>196</v>
       </c>
       <c r="G60" t="s">
@@ -3978,7 +3975,7 @@
       <c r="E61" t="s">
         <v>199</v>
       </c>
-      <c r="F61" s="12" t="s">
+      <c r="F61" s="11" t="s">
         <v>200</v>
       </c>
       <c r="G61" t="s">
@@ -4016,7 +4013,7 @@
       <c r="E62" t="s">
         <v>166</v>
       </c>
-      <c r="F62" s="12" t="s">
+      <c r="F62" s="11" t="s">
         <v>203</v>
       </c>
       <c r="G62" t="s">
@@ -4054,7 +4051,7 @@
       <c r="E63" t="s">
         <v>256</v>
       </c>
-      <c r="F63" s="12" t="s">
+      <c r="F63" s="11" t="s">
         <v>206</v>
       </c>
       <c r="G63" t="s">
@@ -4092,7 +4089,7 @@
       <c r="E64" t="s">
         <v>259</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="F64" s="11" t="s">
         <v>208</v>
       </c>
       <c r="G64" t="s">
@@ -4130,7 +4127,7 @@
       <c r="E65" t="s">
         <v>260</v>
       </c>
-      <c r="F65" s="12" t="s">
+      <c r="F65" s="11" t="s">
         <v>212</v>
       </c>
       <c r="G65" t="s">
@@ -4168,7 +4165,7 @@
       <c r="E66" t="s">
         <v>141</v>
       </c>
-      <c r="F66" s="12" t="s">
+      <c r="F66" s="11" t="s">
         <v>214</v>
       </c>
       <c r="G66" t="s">
@@ -4206,7 +4203,7 @@
       <c r="E67" t="s">
         <v>147</v>
       </c>
-      <c r="F67" s="12" t="s">
+      <c r="F67" s="11" t="s">
         <v>215</v>
       </c>
       <c r="G67" t="s">
@@ -4244,7 +4241,7 @@
       <c r="E68" t="s">
         <v>141</v>
       </c>
-      <c r="F68" s="12" t="s">
+      <c r="F68" s="11" t="s">
         <v>216</v>
       </c>
       <c r="G68" t="s">
@@ -4282,7 +4279,7 @@
       <c r="E69" t="s">
         <v>147</v>
       </c>
-      <c r="F69" s="12" t="s">
+      <c r="F69" s="11" t="s">
         <v>217</v>
       </c>
       <c r="G69" t="s">
@@ -4320,7 +4317,7 @@
       <c r="E70" t="s">
         <v>86</v>
       </c>
-      <c r="F70" s="12" t="s">
+      <c r="F70" s="11" t="s">
         <v>218</v>
       </c>
       <c r="G70" t="s">
@@ -4358,7 +4355,7 @@
       <c r="E71" t="s">
         <v>144</v>
       </c>
-      <c r="F71" s="12" t="s">
+      <c r="F71" s="11" t="s">
         <v>219</v>
       </c>
       <c r="G71" t="s">
@@ -4396,7 +4393,7 @@
       <c r="E72" t="s">
         <v>147</v>
       </c>
-      <c r="F72" s="12" t="s">
+      <c r="F72" s="11" t="s">
         <v>220</v>
       </c>
       <c r="G72" t="s">
@@ -4434,7 +4431,7 @@
       <c r="E73" t="s">
         <v>221</v>
       </c>
-      <c r="F73" s="12" t="s">
+      <c r="F73" s="11" t="s">
         <v>222</v>
       </c>
       <c r="G73" t="s">
@@ -4472,7 +4469,7 @@
       <c r="E74" t="s">
         <v>224</v>
       </c>
-      <c r="F74" s="12" t="s">
+      <c r="F74" s="11" t="s">
         <v>225</v>
       </c>
       <c r="G74" t="s">
@@ -4494,20 +4491,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="8" t="s">
+    <row r="75" spans="1:18" s="16" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A75" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="14"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="8"/>
-      <c r="J75" s="8"/>
-      <c r="K75" s="8"/>
+      <c r="B75" s="17"/>
+      <c r="C75" s="17"/>
+      <c r="D75" s="17"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="18"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+      <c r="K75" s="17"/>
     </row>
     <row r="76" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
@@ -4525,7 +4522,7 @@
       <c r="E76" t="s">
         <v>113</v>
       </c>
-      <c r="F76" s="12" t="s">
+      <c r="F76" s="11" t="s">
         <v>232</v>
       </c>
       <c r="G76" t="s">
@@ -4581,7 +4578,7 @@
       <c r="E77" t="s">
         <v>113</v>
       </c>
-      <c r="F77" s="12" t="s">
+      <c r="F77" s="11" t="s">
         <v>237</v>
       </c>
       <c r="G77" t="s">
@@ -4637,7 +4634,7 @@
       <c r="E78" t="s">
         <v>113</v>
       </c>
-      <c r="F78" s="12" t="s">
+      <c r="F78" s="11" t="s">
         <v>240</v>
       </c>
       <c r="G78" t="s">
@@ -4693,7 +4690,7 @@
       <c r="E79" t="s">
         <v>113</v>
       </c>
-      <c r="F79" s="12" t="s">
+      <c r="F79" s="11" t="s">
         <v>243</v>
       </c>
       <c r="G79" t="s">
@@ -4749,7 +4746,7 @@
       <c r="E80" t="s">
         <v>113</v>
       </c>
-      <c r="F80" s="12" t="s">
+      <c r="F80" s="11" t="s">
         <v>246</v>
       </c>
       <c r="G80" t="s">
@@ -4802,7 +4799,7 @@
       <c r="E81" t="s">
         <v>113</v>
       </c>
-      <c r="F81" s="12" t="s">
+      <c r="F81" s="11" t="s">
         <v>249</v>
       </c>
       <c r="G81" t="s">
@@ -4858,7 +4855,7 @@
       <c r="E82" t="s">
         <v>113</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="F82" s="11" t="s">
         <v>252</v>
       </c>
       <c r="G82" t="s">
@@ -4899,180 +4896,180 @@
       </c>
     </row>
     <row r="83" spans="1:18" ht="13.5" x14ac:dyDescent="0.15">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D83" s="10" t="s">
+      <c r="C83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D83" s="9" t="s">
         <v>281</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="F83" s="15" t="s">
+      <c r="F83" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="G83" s="10" t="s">
+      <c r="G83" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="H83" s="10" t="s">
+      <c r="H83" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I83" s="10">
-        <v>0</v>
-      </c>
-      <c r="J83" s="11"/>
-      <c r="K83" s="10">
-        <v>0</v>
-      </c>
-      <c r="L83" s="11"/>
-      <c r="M83" s="10">
-        <v>0</v>
-      </c>
-      <c r="N83" s="11"/>
-      <c r="O83" s="10">
-        <v>0</v>
-      </c>
-      <c r="P83" s="11"/>
-      <c r="Q83" s="11"/>
-      <c r="R83" s="11"/>
+      <c r="I83" s="9">
+        <v>0</v>
+      </c>
+      <c r="J83" s="10"/>
+      <c r="K83" s="9">
+        <v>0</v>
+      </c>
+      <c r="L83" s="10"/>
+      <c r="M83" s="9">
+        <v>0</v>
+      </c>
+      <c r="N83" s="10"/>
+      <c r="O83" s="9">
+        <v>0</v>
+      </c>
+      <c r="P83" s="10"/>
+      <c r="Q83" s="10"/>
+      <c r="R83" s="10"/>
     </row>
     <row r="84" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D84" s="10" t="s">
+      <c r="C84" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D84" s="9" t="s">
         <v>282</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="F84" s="15" t="s">
+      <c r="F84" s="13" t="s">
         <v>277</v>
       </c>
-      <c r="G84" s="10" t="s">
+      <c r="G84" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="H84" s="10" t="s">
+      <c r="H84" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I84" s="10">
-        <v>0</v>
-      </c>
-      <c r="J84" s="11"/>
-      <c r="K84" s="10">
-        <v>0</v>
-      </c>
-      <c r="L84" s="11"/>
-      <c r="M84" s="10">
-        <v>0</v>
-      </c>
-      <c r="N84" s="11"/>
-      <c r="O84" s="10">
-        <v>0</v>
-      </c>
-      <c r="P84" s="11"/>
-      <c r="Q84" s="11"/>
-      <c r="R84" s="11"/>
+      <c r="I84" s="9">
+        <v>0</v>
+      </c>
+      <c r="J84" s="10"/>
+      <c r="K84" s="9">
+        <v>0</v>
+      </c>
+      <c r="L84" s="10"/>
+      <c r="M84" s="9">
+        <v>0</v>
+      </c>
+      <c r="N84" s="10"/>
+      <c r="O84" s="9">
+        <v>0</v>
+      </c>
+      <c r="P84" s="10"/>
+      <c r="Q84" s="10"/>
+      <c r="R84" s="10"/>
     </row>
     <row r="85" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C85" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D85" s="10" t="s">
+      <c r="C85" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D85" s="9" t="s">
         <v>283</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="9" t="s">
         <v>271</v>
       </c>
-      <c r="F85" s="15" t="s">
+      <c r="F85" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="G85" s="10" t="s">
+      <c r="G85" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="H85" s="10" t="s">
+      <c r="H85" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I85" s="10">
-        <v>0</v>
-      </c>
-      <c r="J85" s="11"/>
-      <c r="K85" s="10">
-        <v>0</v>
-      </c>
-      <c r="L85" s="11"/>
-      <c r="M85" s="10">
-        <v>0</v>
-      </c>
-      <c r="N85" s="11"/>
-      <c r="O85" s="10">
-        <v>0</v>
-      </c>
-      <c r="P85" s="11"/>
-      <c r="Q85" s="11"/>
-      <c r="R85" s="11"/>
+      <c r="I85" s="9">
+        <v>0</v>
+      </c>
+      <c r="J85" s="10"/>
+      <c r="K85" s="9">
+        <v>0</v>
+      </c>
+      <c r="L85" s="10"/>
+      <c r="M85" s="9">
+        <v>0</v>
+      </c>
+      <c r="N85" s="10"/>
+      <c r="O85" s="9">
+        <v>0</v>
+      </c>
+      <c r="P85" s="10"/>
+      <c r="Q85" s="10"/>
+      <c r="R85" s="10"/>
     </row>
     <row r="86" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D86" s="10" t="s">
+      <c r="C86" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="D86" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="E86" s="10" t="s">
+      <c r="E86" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="F86" s="15" t="s">
+      <c r="F86" s="13" t="s">
         <v>279</v>
       </c>
-      <c r="G86" s="10" t="s">
+      <c r="G86" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="H86" s="10" t="s">
+      <c r="H86" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I86" s="10">
-        <v>0</v>
-      </c>
-      <c r="J86" s="11"/>
-      <c r="K86" s="10">
-        <v>0</v>
-      </c>
-      <c r="L86" s="11"/>
-      <c r="M86" s="10">
-        <v>0</v>
-      </c>
-      <c r="N86" s="11"/>
-      <c r="O86" s="10">
-        <v>0</v>
-      </c>
-      <c r="P86" s="11"/>
-      <c r="Q86" s="11"/>
-      <c r="R86" s="11"/>
+      <c r="I86" s="9">
+        <v>0</v>
+      </c>
+      <c r="J86" s="10"/>
+      <c r="K86" s="9">
+        <v>0</v>
+      </c>
+      <c r="L86" s="10"/>
+      <c r="M86" s="9">
+        <v>0</v>
+      </c>
+      <c r="N86" s="10"/>
+      <c r="O86" s="9">
+        <v>0</v>
+      </c>
+      <c r="P86" s="10"/>
+      <c r="Q86" s="10"/>
+      <c r="R86" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:R86" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
